--- a/qtnew/test.xlsx
+++ b/qtnew/test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell\Desktop\qtnew\qtnew\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8B1865D-C758-497A-96A8-C936FA5A066B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BAC5249-B27B-4014-A5F9-15F39610B98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="3030" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
